--- a/artfynd/A 34768-2025 artfynd.xlsx
+++ b/artfynd/A 34768-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2642,6 +2642,1438 @@
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128851793</v>
+      </c>
+      <c r="B20" t="n">
+        <v>75204</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Mårdsundsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>435934</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7004320</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Örtrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128851784</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91494</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Mårdsundsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>436212</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7004096</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Friskt bäckdråg i naturskog</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128851787</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57820</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Mårdsundsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>436100</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7004195</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Gallrad grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128851786</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79116</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Mårdsundsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>435927</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7004337</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Örtrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128851791</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91512</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Mårdsundsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>435967</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7004356</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Gallrad grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128851788</v>
+      </c>
+      <c r="B25" t="n">
+        <v>92818</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Mårdsundsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>436204</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7004134</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Friskt bäckdråg i naturskog</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128851789</v>
+      </c>
+      <c r="B26" t="n">
+        <v>92191</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Mårdsundsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>436183</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7004237</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Fuktigt bäckdråg i naturskog</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128851796</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79116</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Mårdsundsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>436052</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7004106</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Gallrad grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128851785</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91512</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Mårdsundsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>436182</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7004249</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Friskt bäckdråg i naturskog</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128851795</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91512</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Mårdsundsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>436052</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7004105</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Gallrad grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128851792</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91508</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Mårdsundsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>436194</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7004198</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Örtrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128851783</v>
+      </c>
+      <c r="B31" t="n">
+        <v>78093</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Mårdsundsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>435934</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7004320</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Fuktigt bäckdråg i naturskog</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128851790</v>
+      </c>
+      <c r="B32" t="n">
+        <v>88750</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>4405</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Diskvaxskivling</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hygrophorus discoideus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Pers.) Fr.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Mårdsundsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>435918</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7004318</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Futkigt bäckdråg i naturskog</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128851794</v>
+      </c>
+      <c r="B33" t="n">
+        <v>91508</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Mårdsundsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>436047</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7004126</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Örtrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34768-2025 artfynd.xlsx
+++ b/artfynd/A 34768-2025 artfynd.xlsx
@@ -2644,10 +2644,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128851793</v>
+        <v>128851784</v>
       </c>
       <c r="B20" t="n">
-        <v>75204</v>
+        <v>91499</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2655,21 +2655,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2679,10 +2679,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>435934</v>
+        <v>436212</v>
       </c>
       <c r="R20" t="n">
-        <v>7004320</v>
+        <v>7004096</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Örtrik grannaturskog</t>
+          <t>Friskt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2746,10 +2746,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128851784</v>
+        <v>128851793</v>
       </c>
       <c r="B21" t="n">
-        <v>91494</v>
+        <v>75205</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2757,21 +2757,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2781,10 +2781,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436212</v>
+        <v>435934</v>
       </c>
       <c r="R21" t="n">
-        <v>7004096</v>
+        <v>7004320</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Friskt bäckdråg i naturskog</t>
+          <t>Örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2950,10 +2950,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128851786</v>
+        <v>128851791</v>
       </c>
       <c r="B23" t="n">
-        <v>79116</v>
+        <v>91517</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2961,21 +2961,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2985,10 +2985,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>435927</v>
+        <v>435967</v>
       </c>
       <c r="R23" t="n">
-        <v>7004337</v>
+        <v>7004356</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Örtrik grannaturskog</t>
+          <t>Gallrad grannaturskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3052,10 +3052,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128851791</v>
+        <v>128851786</v>
       </c>
       <c r="B24" t="n">
-        <v>91512</v>
+        <v>79120</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3063,21 +3063,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3087,10 +3087,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>435967</v>
+        <v>435927</v>
       </c>
       <c r="R24" t="n">
-        <v>7004356</v>
+        <v>7004337</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Gallrad grannaturskog</t>
+          <t>Örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3157,7 +3157,7 @@
         <v>128851788</v>
       </c>
       <c r="B25" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>128851789</v>
       </c>
       <c r="B26" t="n">
-        <v>92191</v>
+        <v>92196</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3362,10 +3362,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128851796</v>
+        <v>128851785</v>
       </c>
       <c r="B27" t="n">
-        <v>79116</v>
+        <v>91517</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3373,21 +3373,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3397,10 +3397,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436052</v>
+        <v>436182</v>
       </c>
       <c r="R27" t="n">
-        <v>7004106</v>
+        <v>7004249</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3446,7 +3446,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Gallrad grannaturskog</t>
+          <t>Friskt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3464,10 +3464,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128851785</v>
+        <v>128851796</v>
       </c>
       <c r="B28" t="n">
-        <v>91512</v>
+        <v>79120</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3475,21 +3475,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3499,10 +3499,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436182</v>
+        <v>436052</v>
       </c>
       <c r="R28" t="n">
-        <v>7004249</v>
+        <v>7004106</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Friskt bäckdråg i naturskog</t>
+          <t>Gallrad grannaturskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3569,7 +3569,7 @@
         <v>128851795</v>
       </c>
       <c r="B29" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>128851792</v>
       </c>
       <c r="B30" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         <v>128851783</v>
       </c>
       <c r="B31" t="n">
-        <v>78093</v>
+        <v>78097</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3872,32 +3872,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128851790</v>
+        <v>128851794</v>
       </c>
       <c r="B32" t="n">
-        <v>88750</v>
+        <v>91513</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4405</v>
+        <v>1204</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>435918</v>
+        <v>436047</v>
       </c>
       <c r="R32" t="n">
-        <v>7004318</v>
+        <v>7004126</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Futkigt bäckdråg i naturskog</t>
+          <t>Örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -3974,32 +3974,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128851794</v>
+        <v>128851790</v>
       </c>
       <c r="B33" t="n">
-        <v>91508</v>
+        <v>88754</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1204</v>
+        <v>4405</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4009,10 +4009,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436047</v>
+        <v>435918</v>
       </c>
       <c r="R33" t="n">
-        <v>7004126</v>
+        <v>7004318</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Örtrik grannaturskog</t>
+          <t>Futkigt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>

--- a/artfynd/A 34768-2025 artfynd.xlsx
+++ b/artfynd/A 34768-2025 artfynd.xlsx
@@ -2647,7 +2647,7 @@
         <v>128851784</v>
       </c>
       <c r="B20" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2950,10 +2950,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128851791</v>
+        <v>128851786</v>
       </c>
       <c r="B23" t="n">
-        <v>91517</v>
+        <v>79120</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2961,21 +2961,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2985,10 +2985,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>435967</v>
+        <v>435927</v>
       </c>
       <c r="R23" t="n">
-        <v>7004356</v>
+        <v>7004337</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Gallrad grannaturskog</t>
+          <t>Örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3052,45 +3052,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128851786</v>
+        <v>128851788</v>
       </c>
       <c r="B24" t="n">
-        <v>79120</v>
+        <v>92830</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>435927</v>
+        <v>436204</v>
       </c>
       <c r="R24" t="n">
-        <v>7004337</v>
+        <v>7004134</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3131,12 +3134,13 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Örtrik grannaturskog</t>
+          <t>Friskt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3154,48 +3158,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128851788</v>
+        <v>128851791</v>
       </c>
       <c r="B25" t="n">
-        <v>92823</v>
+        <v>91522</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5964</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436204</v>
+        <v>435967</v>
       </c>
       <c r="R25" t="n">
-        <v>7004134</v>
+        <v>7004356</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3236,13 +3237,12 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Friskt bäckdråg i naturskog</t>
+          <t>Gallrad grannaturskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3260,32 +3260,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128851789</v>
+        <v>128851785</v>
       </c>
       <c r="B26" t="n">
-        <v>92196</v>
+        <v>91522</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436183</v>
+        <v>436182</v>
       </c>
       <c r="R26" t="n">
-        <v>7004237</v>
+        <v>7004249</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Fuktigt bäckdråg i naturskog</t>
+          <t>Friskt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3362,10 +3362,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128851785</v>
+        <v>128851796</v>
       </c>
       <c r="B27" t="n">
-        <v>91517</v>
+        <v>79120</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3373,21 +3373,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3397,10 +3397,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436182</v>
+        <v>436052</v>
       </c>
       <c r="R27" t="n">
-        <v>7004249</v>
+        <v>7004106</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3446,7 +3446,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Friskt bäckdråg i naturskog</t>
+          <t>Gallrad grannaturskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3464,32 +3464,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128851796</v>
+        <v>128851789</v>
       </c>
       <c r="B28" t="n">
-        <v>79120</v>
+        <v>92201</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3499,10 +3499,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436052</v>
+        <v>436183</v>
       </c>
       <c r="R28" t="n">
-        <v>7004106</v>
+        <v>7004237</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Gallrad grannaturskog</t>
+          <t>Fuktigt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3569,7 +3569,7 @@
         <v>128851795</v>
       </c>
       <c r="B29" t="n">
-        <v>91517</v>
+        <v>91522</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>128851792</v>
       </c>
       <c r="B30" t="n">
-        <v>91513</v>
+        <v>91518</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>128851794</v>
       </c>
       <c r="B32" t="n">
-        <v>91513</v>
+        <v>91518</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>128851790</v>
       </c>
       <c r="B33" t="n">
-        <v>88754</v>
+        <v>88755</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 34768-2025 artfynd.xlsx
+++ b/artfynd/A 34768-2025 artfynd.xlsx
@@ -2644,10 +2644,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128851784</v>
+        <v>128851793</v>
       </c>
       <c r="B20" t="n">
-        <v>91504</v>
+        <v>75205</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2655,21 +2655,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2679,10 +2679,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436212</v>
+        <v>435934</v>
       </c>
       <c r="R20" t="n">
-        <v>7004096</v>
+        <v>7004320</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Friskt bäckdråg i naturskog</t>
+          <t>Örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2746,10 +2746,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128851793</v>
+        <v>128851784</v>
       </c>
       <c r="B21" t="n">
-        <v>75205</v>
+        <v>91504</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2757,21 +2757,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2781,10 +2781,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>435934</v>
+        <v>436212</v>
       </c>
       <c r="R21" t="n">
-        <v>7004320</v>
+        <v>7004096</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Örtrik grannaturskog</t>
+          <t>Friskt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3260,32 +3260,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128851785</v>
+        <v>128851789</v>
       </c>
       <c r="B26" t="n">
-        <v>91522</v>
+        <v>92201</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436182</v>
+        <v>436183</v>
       </c>
       <c r="R26" t="n">
-        <v>7004249</v>
+        <v>7004237</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Friskt bäckdråg i naturskog</t>
+          <t>Fuktigt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3362,10 +3362,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128851796</v>
+        <v>128851785</v>
       </c>
       <c r="B27" t="n">
-        <v>79120</v>
+        <v>91522</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3373,21 +3373,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3397,10 +3397,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436052</v>
+        <v>436182</v>
       </c>
       <c r="R27" t="n">
-        <v>7004106</v>
+        <v>7004249</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3446,7 +3446,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Gallrad grannaturskog</t>
+          <t>Friskt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3464,32 +3464,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128851789</v>
+        <v>128851796</v>
       </c>
       <c r="B28" t="n">
-        <v>92201</v>
+        <v>79120</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3499,10 +3499,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436183</v>
+        <v>436052</v>
       </c>
       <c r="R28" t="n">
-        <v>7004237</v>
+        <v>7004106</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Fuktigt bäckdråg i naturskog</t>
+          <t>Gallrad grannaturskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>

--- a/artfynd/A 34768-2025 artfynd.xlsx
+++ b/artfynd/A 34768-2025 artfynd.xlsx
@@ -2644,10 +2644,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128851793</v>
+        <v>128851784</v>
       </c>
       <c r="B20" t="n">
-        <v>75205</v>
+        <v>91504</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2655,21 +2655,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2679,10 +2679,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>435934</v>
+        <v>436212</v>
       </c>
       <c r="R20" t="n">
-        <v>7004320</v>
+        <v>7004096</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Örtrik grannaturskog</t>
+          <t>Friskt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2746,10 +2746,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128851784</v>
+        <v>128851793</v>
       </c>
       <c r="B21" t="n">
-        <v>91504</v>
+        <v>75205</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2757,21 +2757,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2781,10 +2781,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436212</v>
+        <v>435934</v>
       </c>
       <c r="R21" t="n">
-        <v>7004096</v>
+        <v>7004320</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Friskt bäckdråg i naturskog</t>
+          <t>Örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2950,10 +2950,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128851786</v>
+        <v>128851791</v>
       </c>
       <c r="B23" t="n">
-        <v>79120</v>
+        <v>91522</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2961,21 +2961,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2985,10 +2985,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>435927</v>
+        <v>435967</v>
       </c>
       <c r="R23" t="n">
-        <v>7004337</v>
+        <v>7004356</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Örtrik grannaturskog</t>
+          <t>Gallrad grannaturskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3158,10 +3158,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128851791</v>
+        <v>128851786</v>
       </c>
       <c r="B25" t="n">
-        <v>91522</v>
+        <v>79120</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3169,21 +3169,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>435967</v>
+        <v>435927</v>
       </c>
       <c r="R25" t="n">
-        <v>7004356</v>
+        <v>7004337</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Gallrad grannaturskog</t>
+          <t>Örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3872,32 +3872,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128851794</v>
+        <v>128851790</v>
       </c>
       <c r="B32" t="n">
-        <v>91518</v>
+        <v>88755</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1204</v>
+        <v>4405</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436047</v>
+        <v>435918</v>
       </c>
       <c r="R32" t="n">
-        <v>7004126</v>
+        <v>7004318</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Örtrik grannaturskog</t>
+          <t>Futkigt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -3974,32 +3974,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128851790</v>
+        <v>128851794</v>
       </c>
       <c r="B33" t="n">
-        <v>88755</v>
+        <v>91518</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4405</v>
+        <v>1204</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4009,10 +4009,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>435918</v>
+        <v>436047</v>
       </c>
       <c r="R33" t="n">
-        <v>7004318</v>
+        <v>7004126</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Futkigt bäckdråg i naturskog</t>
+          <t>Örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>

--- a/artfynd/A 34768-2025 artfynd.xlsx
+++ b/artfynd/A 34768-2025 artfynd.xlsx
@@ -2647,7 +2647,7 @@
         <v>128851784</v>
       </c>
       <c r="B20" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>128851793</v>
       </c>
       <c r="B21" t="n">
-        <v>75205</v>
+        <v>75209</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>128851787</v>
       </c>
       <c r="B22" t="n">
-        <v>57820</v>
+        <v>57824</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>128851791</v>
       </c>
       <c r="B23" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3052,48 +3052,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128851788</v>
+        <v>128851786</v>
       </c>
       <c r="B24" t="n">
-        <v>92830</v>
+        <v>79124</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436204</v>
+        <v>435927</v>
       </c>
       <c r="R24" t="n">
-        <v>7004134</v>
+        <v>7004337</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3134,13 +3131,12 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Friskt bäckdråg i naturskog</t>
+          <t>Örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3158,45 +3154,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128851786</v>
+        <v>128851788</v>
       </c>
       <c r="B25" t="n">
-        <v>79120</v>
+        <v>92834</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>435927</v>
+        <v>436204</v>
       </c>
       <c r="R25" t="n">
-        <v>7004337</v>
+        <v>7004134</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3237,12 +3236,13 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Örtrik grannaturskog</t>
+          <t>Friskt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3260,32 +3260,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128851789</v>
+        <v>128851785</v>
       </c>
       <c r="B26" t="n">
-        <v>92201</v>
+        <v>91526</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436183</v>
+        <v>436182</v>
       </c>
       <c r="R26" t="n">
-        <v>7004237</v>
+        <v>7004249</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Fuktigt bäckdråg i naturskog</t>
+          <t>Friskt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3362,10 +3362,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128851785</v>
+        <v>128851796</v>
       </c>
       <c r="B27" t="n">
-        <v>91522</v>
+        <v>79124</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3373,21 +3373,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3397,10 +3397,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436182</v>
+        <v>436052</v>
       </c>
       <c r="R27" t="n">
-        <v>7004249</v>
+        <v>7004106</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3446,7 +3446,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Friskt bäckdråg i naturskog</t>
+          <t>Gallrad grannaturskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3464,32 +3464,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128851796</v>
+        <v>128851789</v>
       </c>
       <c r="B28" t="n">
-        <v>79120</v>
+        <v>92205</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3499,10 +3499,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436052</v>
+        <v>436183</v>
       </c>
       <c r="R28" t="n">
-        <v>7004106</v>
+        <v>7004237</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Gallrad grannaturskog</t>
+          <t>Fuktigt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3569,7 +3569,7 @@
         <v>128851795</v>
       </c>
       <c r="B29" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>128851792</v>
       </c>
       <c r="B30" t="n">
-        <v>91518</v>
+        <v>91522</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         <v>128851783</v>
       </c>
       <c r="B31" t="n">
-        <v>78097</v>
+        <v>78101</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3872,32 +3872,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128851790</v>
+        <v>128851794</v>
       </c>
       <c r="B32" t="n">
-        <v>88755</v>
+        <v>91522</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4405</v>
+        <v>1204</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>435918</v>
+        <v>436047</v>
       </c>
       <c r="R32" t="n">
-        <v>7004318</v>
+        <v>7004126</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Futkigt bäckdråg i naturskog</t>
+          <t>Örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -3974,32 +3974,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128851794</v>
+        <v>128851790</v>
       </c>
       <c r="B33" t="n">
-        <v>91518</v>
+        <v>88759</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1204</v>
+        <v>4405</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4009,10 +4009,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436047</v>
+        <v>435918</v>
       </c>
       <c r="R33" t="n">
-        <v>7004126</v>
+        <v>7004318</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Örtrik grannaturskog</t>
+          <t>Futkigt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>

--- a/artfynd/A 34768-2025 artfynd.xlsx
+++ b/artfynd/A 34768-2025 artfynd.xlsx
@@ -2644,10 +2644,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128851784</v>
+        <v>128851793</v>
       </c>
       <c r="B20" t="n">
-        <v>91508</v>
+        <v>75209</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2655,21 +2655,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2679,10 +2679,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436212</v>
+        <v>435934</v>
       </c>
       <c r="R20" t="n">
-        <v>7004096</v>
+        <v>7004320</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Friskt bäckdråg i naturskog</t>
+          <t>Örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2746,10 +2746,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128851793</v>
+        <v>128851784</v>
       </c>
       <c r="B21" t="n">
-        <v>75209</v>
+        <v>91508</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2757,21 +2757,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2781,10 +2781,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>435934</v>
+        <v>436212</v>
       </c>
       <c r="R21" t="n">
-        <v>7004320</v>
+        <v>7004096</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Örtrik grannaturskog</t>
+          <t>Friskt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3052,45 +3052,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128851786</v>
+        <v>128851788</v>
       </c>
       <c r="B24" t="n">
-        <v>79124</v>
+        <v>92834</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>435927</v>
+        <v>436204</v>
       </c>
       <c r="R24" t="n">
-        <v>7004337</v>
+        <v>7004134</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3131,12 +3134,13 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Örtrik grannaturskog</t>
+          <t>Friskt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3154,48 +3158,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128851788</v>
+        <v>128851786</v>
       </c>
       <c r="B25" t="n">
-        <v>92834</v>
+        <v>79124</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436204</v>
+        <v>435927</v>
       </c>
       <c r="R25" t="n">
-        <v>7004134</v>
+        <v>7004337</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3236,13 +3237,12 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Friskt bäckdråg i naturskog</t>
+          <t>Örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3260,10 +3260,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128851785</v>
+        <v>128851796</v>
       </c>
       <c r="B26" t="n">
-        <v>91526</v>
+        <v>79124</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3271,21 +3271,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436182</v>
+        <v>436052</v>
       </c>
       <c r="R26" t="n">
-        <v>7004249</v>
+        <v>7004106</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Friskt bäckdråg i naturskog</t>
+          <t>Gallrad grannaturskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3362,32 +3362,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128851796</v>
+        <v>128851789</v>
       </c>
       <c r="B27" t="n">
-        <v>79124</v>
+        <v>92205</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3397,10 +3397,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436052</v>
+        <v>436183</v>
       </c>
       <c r="R27" t="n">
-        <v>7004106</v>
+        <v>7004237</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3446,7 +3446,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Gallrad grannaturskog</t>
+          <t>Fuktigt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3464,32 +3464,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128851789</v>
+        <v>128851785</v>
       </c>
       <c r="B28" t="n">
-        <v>92205</v>
+        <v>91526</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3499,10 +3499,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436183</v>
+        <v>436182</v>
       </c>
       <c r="R28" t="n">
-        <v>7004237</v>
+        <v>7004249</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Fuktigt bäckdråg i naturskog</t>
+          <t>Friskt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3872,32 +3872,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128851794</v>
+        <v>128851790</v>
       </c>
       <c r="B32" t="n">
-        <v>91522</v>
+        <v>88759</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1204</v>
+        <v>4405</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436047</v>
+        <v>435918</v>
       </c>
       <c r="R32" t="n">
-        <v>7004126</v>
+        <v>7004318</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Örtrik grannaturskog</t>
+          <t>Futkigt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -3974,32 +3974,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128851790</v>
+        <v>128851794</v>
       </c>
       <c r="B33" t="n">
-        <v>88759</v>
+        <v>91522</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4405</v>
+        <v>1204</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4009,10 +4009,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>435918</v>
+        <v>436047</v>
       </c>
       <c r="R33" t="n">
-        <v>7004318</v>
+        <v>7004126</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Futkigt bäckdråg i naturskog</t>
+          <t>Örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>

--- a/artfynd/A 34768-2025 artfynd.xlsx
+++ b/artfynd/A 34768-2025 artfynd.xlsx
@@ -2950,45 +2950,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128851791</v>
+        <v>128851788</v>
       </c>
       <c r="B23" t="n">
-        <v>91526</v>
+        <v>92834</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>5964</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>435967</v>
+        <v>436204</v>
       </c>
       <c r="R23" t="n">
-        <v>7004356</v>
+        <v>7004134</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3029,12 +3032,13 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Gallrad grannaturskog</t>
+          <t>Friskt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3052,48 +3056,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128851788</v>
+        <v>128851786</v>
       </c>
       <c r="B24" t="n">
-        <v>92834</v>
+        <v>79124</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436204</v>
+        <v>435927</v>
       </c>
       <c r="R24" t="n">
-        <v>7004134</v>
+        <v>7004337</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3134,13 +3135,12 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Friskt bäckdråg i naturskog</t>
+          <t>Örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3158,10 +3158,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128851786</v>
+        <v>128851791</v>
       </c>
       <c r="B25" t="n">
-        <v>79124</v>
+        <v>91526</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3169,21 +3169,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>435927</v>
+        <v>435967</v>
       </c>
       <c r="R25" t="n">
-        <v>7004337</v>
+        <v>7004356</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Örtrik grannaturskog</t>
+          <t>Gallrad grannaturskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3260,32 +3260,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128851796</v>
+        <v>128851789</v>
       </c>
       <c r="B26" t="n">
-        <v>79124</v>
+        <v>92205</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436052</v>
+        <v>436183</v>
       </c>
       <c r="R26" t="n">
-        <v>7004106</v>
+        <v>7004237</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Gallrad grannaturskog</t>
+          <t>Fuktigt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3362,32 +3362,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128851789</v>
+        <v>128851796</v>
       </c>
       <c r="B27" t="n">
-        <v>92205</v>
+        <v>79124</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3397,10 +3397,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436183</v>
+        <v>436052</v>
       </c>
       <c r="R27" t="n">
-        <v>7004237</v>
+        <v>7004106</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3446,7 +3446,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Fuktigt bäckdråg i naturskog</t>
+          <t>Gallrad grannaturskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>

--- a/artfynd/A 34768-2025 artfynd.xlsx
+++ b/artfynd/A 34768-2025 artfynd.xlsx
@@ -2647,7 +2647,7 @@
         <v>128851793</v>
       </c>
       <c r="B20" t="n">
-        <v>75209</v>
+        <v>83005</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>128851784</v>
       </c>
       <c r="B21" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>128851787</v>
       </c>
       <c r="B22" t="n">
-        <v>57824</v>
+        <v>57827</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2950,48 +2950,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128851788</v>
+        <v>128851791</v>
       </c>
       <c r="B23" t="n">
-        <v>92834</v>
+        <v>91531</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5964</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436204</v>
+        <v>435967</v>
       </c>
       <c r="R23" t="n">
-        <v>7004134</v>
+        <v>7004356</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3032,13 +3029,12 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Friskt bäckdråg i naturskog</t>
+          <t>Gallrad grannaturskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3059,7 +3055,7 @@
         <v>128851786</v>
       </c>
       <c r="B24" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3158,45 +3154,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128851791</v>
+        <v>128851788</v>
       </c>
       <c r="B25" t="n">
-        <v>91526</v>
+        <v>92839</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>5964</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>435967</v>
+        <v>436204</v>
       </c>
       <c r="R25" t="n">
-        <v>7004356</v>
+        <v>7004134</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3237,12 +3236,13 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Gallrad grannaturskog</t>
+          <t>Friskt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3263,7 +3263,7 @@
         <v>128851789</v>
       </c>
       <c r="B26" t="n">
-        <v>92205</v>
+        <v>92210</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3362,10 +3362,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128851796</v>
+        <v>128851785</v>
       </c>
       <c r="B27" t="n">
-        <v>79124</v>
+        <v>91531</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3373,21 +3373,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3397,10 +3397,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436052</v>
+        <v>436182</v>
       </c>
       <c r="R27" t="n">
-        <v>7004106</v>
+        <v>7004249</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3446,7 +3446,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Gallrad grannaturskog</t>
+          <t>Friskt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3464,10 +3464,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128851785</v>
+        <v>128851796</v>
       </c>
       <c r="B28" t="n">
-        <v>91526</v>
+        <v>79029</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3475,21 +3475,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3499,10 +3499,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436182</v>
+        <v>436052</v>
       </c>
       <c r="R28" t="n">
-        <v>7004249</v>
+        <v>7004106</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Friskt bäckdråg i naturskog</t>
+          <t>Gallrad grannaturskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3569,7 +3569,7 @@
         <v>128851795</v>
       </c>
       <c r="B29" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>128851792</v>
       </c>
       <c r="B30" t="n">
-        <v>91522</v>
+        <v>91527</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         <v>128851783</v>
       </c>
       <c r="B31" t="n">
-        <v>78101</v>
+        <v>78042</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>128851790</v>
       </c>
       <c r="B32" t="n">
-        <v>88759</v>
+        <v>88764</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>128851794</v>
       </c>
       <c r="B33" t="n">
-        <v>91522</v>
+        <v>91527</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 34768-2025 artfynd.xlsx
+++ b/artfynd/A 34768-2025 artfynd.xlsx
@@ -2950,45 +2950,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128851786</v>
+        <v>128851788</v>
       </c>
       <c r="B23" t="n">
-        <v>79034</v>
+        <v>92847</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>435927</v>
+        <v>436204</v>
       </c>
       <c r="R23" t="n">
-        <v>7004337</v>
+        <v>7004134</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3029,12 +3032,13 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Örtrik grannaturskog</t>
+          <t>Friskt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3052,10 +3056,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128851791</v>
+        <v>128851786</v>
       </c>
       <c r="B24" t="n">
-        <v>91538</v>
+        <v>79034</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3063,21 +3067,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3087,10 +3091,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>435967</v>
+        <v>435927</v>
       </c>
       <c r="R24" t="n">
-        <v>7004356</v>
+        <v>7004337</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3136,7 +3140,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Gallrad grannaturskog</t>
+          <t>Örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3154,48 +3158,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128851788</v>
+        <v>128851791</v>
       </c>
       <c r="B25" t="n">
-        <v>92847</v>
+        <v>91538</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5964</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436204</v>
+        <v>435967</v>
       </c>
       <c r="R25" t="n">
-        <v>7004134</v>
+        <v>7004356</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3236,13 +3237,12 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Friskt bäckdråg i naturskog</t>
+          <t>Gallrad grannaturskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>

--- a/artfynd/A 34768-2025 artfynd.xlsx
+++ b/artfynd/A 34768-2025 artfynd.xlsx
@@ -2644,10 +2644,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128851793</v>
+        <v>128851784</v>
       </c>
       <c r="B20" t="n">
-        <v>83010</v>
+        <v>91523</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2655,21 +2655,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2679,10 +2679,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>435934</v>
+        <v>436212</v>
       </c>
       <c r="R20" t="n">
-        <v>7004320</v>
+        <v>7004096</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Örtrik grannaturskog</t>
+          <t>Friskt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2746,10 +2746,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128851784</v>
+        <v>128851793</v>
       </c>
       <c r="B21" t="n">
-        <v>91520</v>
+        <v>83010</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2757,21 +2757,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2781,10 +2781,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436212</v>
+        <v>435934</v>
       </c>
       <c r="R21" t="n">
-        <v>7004096</v>
+        <v>7004320</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Friskt bäckdråg i naturskog</t>
+          <t>Örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2950,48 +2950,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128851788</v>
+        <v>128851786</v>
       </c>
       <c r="B23" t="n">
-        <v>92847</v>
+        <v>79034</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436204</v>
+        <v>435927</v>
       </c>
       <c r="R23" t="n">
-        <v>7004134</v>
+        <v>7004337</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3032,13 +3029,12 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Friskt bäckdråg i naturskog</t>
+          <t>Örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3056,10 +3052,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128851786</v>
+        <v>128851791</v>
       </c>
       <c r="B24" t="n">
-        <v>79034</v>
+        <v>91541</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3067,21 +3063,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3091,10 +3087,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>435927</v>
+        <v>435967</v>
       </c>
       <c r="R24" t="n">
-        <v>7004337</v>
+        <v>7004356</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3140,7 +3136,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Örtrik grannaturskog</t>
+          <t>Gallrad grannaturskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3158,45 +3154,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128851791</v>
+        <v>128851788</v>
       </c>
       <c r="B25" t="n">
-        <v>91538</v>
+        <v>92852</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>5964</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>435967</v>
+        <v>436204</v>
       </c>
       <c r="R25" t="n">
-        <v>7004356</v>
+        <v>7004134</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3237,12 +3236,13 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Gallrad grannaturskog</t>
+          <t>Friskt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3260,32 +3260,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128851785</v>
+        <v>128851789</v>
       </c>
       <c r="B26" t="n">
-        <v>91538</v>
+        <v>92223</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436182</v>
+        <v>436183</v>
       </c>
       <c r="R26" t="n">
-        <v>7004249</v>
+        <v>7004237</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Friskt bäckdråg i naturskog</t>
+          <t>Fuktigt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3362,32 +3362,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128851789</v>
+        <v>128851785</v>
       </c>
       <c r="B27" t="n">
-        <v>92218</v>
+        <v>91541</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3397,10 +3397,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436183</v>
+        <v>436182</v>
       </c>
       <c r="R27" t="n">
-        <v>7004237</v>
+        <v>7004249</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3446,7 +3446,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Fuktigt bäckdråg i naturskog</t>
+          <t>Friskt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3569,7 +3569,7 @@
         <v>128851795</v>
       </c>
       <c r="B29" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>128851792</v>
       </c>
       <c r="B30" t="n">
-        <v>91534</v>
+        <v>91537</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3872,32 +3872,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128851794</v>
+        <v>128851790</v>
       </c>
       <c r="B32" t="n">
-        <v>91534</v>
+        <v>88774</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1204</v>
+        <v>4405</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436047</v>
+        <v>435918</v>
       </c>
       <c r="R32" t="n">
-        <v>7004126</v>
+        <v>7004318</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Örtrik grannaturskog</t>
+          <t>Futkigt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -3974,32 +3974,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128851790</v>
+        <v>128851794</v>
       </c>
       <c r="B33" t="n">
-        <v>88771</v>
+        <v>91537</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4405</v>
+        <v>1204</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4009,10 +4009,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>435918</v>
+        <v>436047</v>
       </c>
       <c r="R33" t="n">
-        <v>7004318</v>
+        <v>7004126</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Futkigt bäckdråg i naturskog</t>
+          <t>Örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>

--- a/artfynd/A 34768-2025 artfynd.xlsx
+++ b/artfynd/A 34768-2025 artfynd.xlsx
@@ -2644,10 +2644,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128851784</v>
+        <v>128851793</v>
       </c>
       <c r="B20" t="n">
-        <v>91523</v>
+        <v>83011</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2655,21 +2655,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2679,10 +2679,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436212</v>
+        <v>435934</v>
       </c>
       <c r="R20" t="n">
-        <v>7004096</v>
+        <v>7004320</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Friskt bäckdråg i naturskog</t>
+          <t>Örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2746,10 +2746,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128851793</v>
+        <v>128851784</v>
       </c>
       <c r="B21" t="n">
-        <v>83010</v>
+        <v>91526</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2757,21 +2757,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2781,10 +2781,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>435934</v>
+        <v>436212</v>
       </c>
       <c r="R21" t="n">
-        <v>7004320</v>
+        <v>7004096</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Örtrik grannaturskog</t>
+          <t>Friskt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2953,7 +2953,7 @@
         <v>128851786</v>
       </c>
       <c r="B23" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>128851791</v>
       </c>
       <c r="B24" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>128851788</v>
       </c>
       <c r="B25" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3260,32 +3260,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128851789</v>
+        <v>128851796</v>
       </c>
       <c r="B26" t="n">
-        <v>92223</v>
+        <v>79035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436183</v>
+        <v>436052</v>
       </c>
       <c r="R26" t="n">
-        <v>7004237</v>
+        <v>7004106</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Fuktigt bäckdråg i naturskog</t>
+          <t>Gallrad grannaturskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3362,32 +3362,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128851785</v>
+        <v>128851789</v>
       </c>
       <c r="B27" t="n">
-        <v>91541</v>
+        <v>92226</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3397,10 +3397,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436182</v>
+        <v>436183</v>
       </c>
       <c r="R27" t="n">
-        <v>7004249</v>
+        <v>7004237</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3446,7 +3446,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Friskt bäckdråg i naturskog</t>
+          <t>Fuktigt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3464,10 +3464,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128851796</v>
+        <v>128851785</v>
       </c>
       <c r="B28" t="n">
-        <v>79034</v>
+        <v>91544</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3475,21 +3475,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3499,10 +3499,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436052</v>
+        <v>436182</v>
       </c>
       <c r="R28" t="n">
-        <v>7004106</v>
+        <v>7004249</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Gallrad grannaturskog</t>
+          <t>Friskt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3569,7 +3569,7 @@
         <v>128851795</v>
       </c>
       <c r="B29" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>128851792</v>
       </c>
       <c r="B30" t="n">
-        <v>91537</v>
+        <v>91540</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         <v>128851783</v>
       </c>
       <c r="B31" t="n">
-        <v>78047</v>
+        <v>78048</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>128851790</v>
       </c>
       <c r="B32" t="n">
-        <v>88774</v>
+        <v>88777</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>128851794</v>
       </c>
       <c r="B33" t="n">
-        <v>91537</v>
+        <v>91540</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 34768-2025 artfynd.xlsx
+++ b/artfynd/A 34768-2025 artfynd.xlsx
@@ -2950,10 +2950,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128851786</v>
+        <v>128851791</v>
       </c>
       <c r="B23" t="n">
-        <v>79035</v>
+        <v>91544</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2961,21 +2961,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2985,10 +2985,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>435927</v>
+        <v>435967</v>
       </c>
       <c r="R23" t="n">
-        <v>7004337</v>
+        <v>7004356</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Örtrik grannaturskog</t>
+          <t>Gallrad grannaturskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3052,45 +3052,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128851791</v>
+        <v>128851788</v>
       </c>
       <c r="B24" t="n">
-        <v>91544</v>
+        <v>92855</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>5964</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>435967</v>
+        <v>436204</v>
       </c>
       <c r="R24" t="n">
-        <v>7004356</v>
+        <v>7004134</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3131,12 +3134,13 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Gallrad grannaturskog</t>
+          <t>Friskt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3154,48 +3158,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128851788</v>
+        <v>128851786</v>
       </c>
       <c r="B25" t="n">
-        <v>92855</v>
+        <v>79035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436204</v>
+        <v>435927</v>
       </c>
       <c r="R25" t="n">
-        <v>7004134</v>
+        <v>7004337</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3236,13 +3237,12 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Friskt bäckdråg i naturskog</t>
+          <t>Örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3260,32 +3260,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128851796</v>
+        <v>128851789</v>
       </c>
       <c r="B26" t="n">
-        <v>79035</v>
+        <v>92226</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436052</v>
+        <v>436183</v>
       </c>
       <c r="R26" t="n">
-        <v>7004106</v>
+        <v>7004237</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Gallrad grannaturskog</t>
+          <t>Fuktigt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3362,32 +3362,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128851789</v>
+        <v>128851785</v>
       </c>
       <c r="B27" t="n">
-        <v>92226</v>
+        <v>91544</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3397,10 +3397,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436183</v>
+        <v>436182</v>
       </c>
       <c r="R27" t="n">
-        <v>7004237</v>
+        <v>7004249</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3446,7 +3446,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Fuktigt bäckdråg i naturskog</t>
+          <t>Friskt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3464,10 +3464,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128851785</v>
+        <v>128851796</v>
       </c>
       <c r="B28" t="n">
-        <v>91544</v>
+        <v>79035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3475,21 +3475,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3499,10 +3499,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436182</v>
+        <v>436052</v>
       </c>
       <c r="R28" t="n">
-        <v>7004249</v>
+        <v>7004106</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Friskt bäckdråg i naturskog</t>
+          <t>Gallrad grannaturskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>

--- a/artfynd/A 34768-2025 artfynd.xlsx
+++ b/artfynd/A 34768-2025 artfynd.xlsx
@@ -2644,10 +2644,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128851793</v>
+        <v>128851784</v>
       </c>
       <c r="B20" t="n">
-        <v>83011</v>
+        <v>91526</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2655,21 +2655,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2679,10 +2679,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>435934</v>
+        <v>436212</v>
       </c>
       <c r="R20" t="n">
-        <v>7004320</v>
+        <v>7004096</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Örtrik grannaturskog</t>
+          <t>Friskt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2746,10 +2746,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128851784</v>
+        <v>128851793</v>
       </c>
       <c r="B21" t="n">
-        <v>91526</v>
+        <v>83011</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2757,21 +2757,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2781,10 +2781,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436212</v>
+        <v>435934</v>
       </c>
       <c r="R21" t="n">
-        <v>7004096</v>
+        <v>7004320</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Friskt bäckdråg i naturskog</t>
+          <t>Örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>

--- a/artfynd/A 34768-2025 artfynd.xlsx
+++ b/artfynd/A 34768-2025 artfynd.xlsx
@@ -2644,10 +2644,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128851784</v>
+        <v>128851793</v>
       </c>
       <c r="B20" t="n">
-        <v>91526</v>
+        <v>83011</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2655,21 +2655,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2679,10 +2679,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436212</v>
+        <v>435934</v>
       </c>
       <c r="R20" t="n">
-        <v>7004096</v>
+        <v>7004320</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Friskt bäckdråg i naturskog</t>
+          <t>Örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2746,10 +2746,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128851793</v>
+        <v>128851784</v>
       </c>
       <c r="B21" t="n">
-        <v>83011</v>
+        <v>91526</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2757,21 +2757,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2781,10 +2781,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>435934</v>
+        <v>436212</v>
       </c>
       <c r="R21" t="n">
-        <v>7004320</v>
+        <v>7004096</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Örtrik grannaturskog</t>
+          <t>Friskt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3872,32 +3872,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128851790</v>
+        <v>128851794</v>
       </c>
       <c r="B32" t="n">
-        <v>88777</v>
+        <v>91540</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4405</v>
+        <v>1204</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>435918</v>
+        <v>436047</v>
       </c>
       <c r="R32" t="n">
-        <v>7004318</v>
+        <v>7004126</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Futkigt bäckdråg i naturskog</t>
+          <t>Örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -3974,32 +3974,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128851794</v>
+        <v>128851790</v>
       </c>
       <c r="B33" t="n">
-        <v>91540</v>
+        <v>88777</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1204</v>
+        <v>4405</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4009,10 +4009,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436047</v>
+        <v>435918</v>
       </c>
       <c r="R33" t="n">
-        <v>7004126</v>
+        <v>7004318</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Örtrik grannaturskog</t>
+          <t>Futkigt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>

--- a/artfynd/A 34768-2025 artfynd.xlsx
+++ b/artfynd/A 34768-2025 artfynd.xlsx
@@ -2647,7 +2647,7 @@
         <v>128851793</v>
       </c>
       <c r="B20" t="n">
-        <v>83011</v>
+        <v>83015</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>128851784</v>
       </c>
       <c r="B21" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>128851787</v>
       </c>
       <c r="B22" t="n">
-        <v>57827</v>
+        <v>57829</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2950,45 +2950,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128851791</v>
+        <v>128851788</v>
       </c>
       <c r="B23" t="n">
-        <v>91544</v>
+        <v>92862</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>5964</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>435967</v>
+        <v>436204</v>
       </c>
       <c r="R23" t="n">
-        <v>7004356</v>
+        <v>7004134</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3029,12 +3032,13 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Gallrad grannaturskog</t>
+          <t>Friskt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3052,48 +3056,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128851788</v>
+        <v>128851791</v>
       </c>
       <c r="B24" t="n">
-        <v>92855</v>
+        <v>91551</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5964</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436204</v>
+        <v>435967</v>
       </c>
       <c r="R24" t="n">
-        <v>7004134</v>
+        <v>7004356</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3134,13 +3135,12 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Friskt bäckdråg i naturskog</t>
+          <t>Gallrad grannaturskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3161,7 +3161,7 @@
         <v>128851786</v>
       </c>
       <c r="B25" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3260,32 +3260,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128851789</v>
+        <v>128851785</v>
       </c>
       <c r="B26" t="n">
-        <v>92226</v>
+        <v>91551</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436183</v>
+        <v>436182</v>
       </c>
       <c r="R26" t="n">
-        <v>7004237</v>
+        <v>7004249</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Fuktigt bäckdråg i naturskog</t>
+          <t>Friskt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3362,10 +3362,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128851785</v>
+        <v>128851796</v>
       </c>
       <c r="B27" t="n">
-        <v>91544</v>
+        <v>79039</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3373,21 +3373,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3397,10 +3397,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436182</v>
+        <v>436052</v>
       </c>
       <c r="R27" t="n">
-        <v>7004249</v>
+        <v>7004106</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3446,7 +3446,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Friskt bäckdråg i naturskog</t>
+          <t>Gallrad grannaturskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3464,32 +3464,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128851796</v>
+        <v>128851789</v>
       </c>
       <c r="B28" t="n">
-        <v>79035</v>
+        <v>92233</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3499,10 +3499,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436052</v>
+        <v>436183</v>
       </c>
       <c r="R28" t="n">
-        <v>7004106</v>
+        <v>7004237</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Gallrad grannaturskog</t>
+          <t>Fuktigt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3569,7 +3569,7 @@
         <v>128851795</v>
       </c>
       <c r="B29" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>128851792</v>
       </c>
       <c r="B30" t="n">
-        <v>91540</v>
+        <v>91547</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         <v>128851783</v>
       </c>
       <c r="B31" t="n">
-        <v>78048</v>
+        <v>78052</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>128851794</v>
       </c>
       <c r="B32" t="n">
-        <v>91540</v>
+        <v>91547</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>128851790</v>
       </c>
       <c r="B33" t="n">
-        <v>88777</v>
+        <v>88781</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 34768-2025 artfynd.xlsx
+++ b/artfynd/A 34768-2025 artfynd.xlsx
@@ -2950,48 +2950,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128851788</v>
+        <v>128851786</v>
       </c>
       <c r="B23" t="n">
-        <v>92862</v>
+        <v>79039</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436204</v>
+        <v>435927</v>
       </c>
       <c r="R23" t="n">
-        <v>7004134</v>
+        <v>7004337</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3032,13 +3029,12 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Friskt bäckdråg i naturskog</t>
+          <t>Örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3158,45 +3154,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128851786</v>
+        <v>128851788</v>
       </c>
       <c r="B25" t="n">
-        <v>79039</v>
+        <v>92862</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>435927</v>
+        <v>436204</v>
       </c>
       <c r="R25" t="n">
-        <v>7004337</v>
+        <v>7004134</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3237,12 +3236,13 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Örtrik grannaturskog</t>
+          <t>Friskt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3260,32 +3260,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128851785</v>
+        <v>128851789</v>
       </c>
       <c r="B26" t="n">
-        <v>91551</v>
+        <v>92233</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436182</v>
+        <v>436183</v>
       </c>
       <c r="R26" t="n">
-        <v>7004249</v>
+        <v>7004237</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Friskt bäckdråg i naturskog</t>
+          <t>Fuktigt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3464,32 +3464,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128851789</v>
+        <v>128851785</v>
       </c>
       <c r="B28" t="n">
-        <v>92233</v>
+        <v>91551</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3499,10 +3499,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436183</v>
+        <v>436182</v>
       </c>
       <c r="R28" t="n">
-        <v>7004237</v>
+        <v>7004249</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Fuktigt bäckdråg i naturskog</t>
+          <t>Friskt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>

--- a/artfynd/A 34768-2025 artfynd.xlsx
+++ b/artfynd/A 34768-2025 artfynd.xlsx
@@ -2644,10 +2644,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128851793</v>
+        <v>128851784</v>
       </c>
       <c r="B20" t="n">
-        <v>83015</v>
+        <v>91540</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2655,21 +2655,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2679,10 +2679,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>435934</v>
+        <v>436212</v>
       </c>
       <c r="R20" t="n">
-        <v>7004320</v>
+        <v>7004096</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Örtrik grannaturskog</t>
+          <t>Friskt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2746,10 +2746,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128851784</v>
+        <v>128851793</v>
       </c>
       <c r="B21" t="n">
-        <v>91533</v>
+        <v>83005</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2757,21 +2757,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2781,10 +2781,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436212</v>
+        <v>435934</v>
       </c>
       <c r="R21" t="n">
-        <v>7004096</v>
+        <v>7004320</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Friskt bäckdråg i naturskog</t>
+          <t>Örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2950,45 +2950,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128851786</v>
+        <v>128851788</v>
       </c>
       <c r="B23" t="n">
-        <v>79039</v>
+        <v>92869</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>435927</v>
+        <v>436204</v>
       </c>
       <c r="R23" t="n">
-        <v>7004337</v>
+        <v>7004134</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3029,12 +3032,13 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Örtrik grannaturskog</t>
+          <t>Friskt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3055,7 +3059,7 @@
         <v>128851791</v>
       </c>
       <c r="B24" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3154,48 +3158,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128851788</v>
+        <v>128851786</v>
       </c>
       <c r="B25" t="n">
-        <v>92862</v>
+        <v>79039</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436204</v>
+        <v>435927</v>
       </c>
       <c r="R25" t="n">
-        <v>7004134</v>
+        <v>7004337</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3236,13 +3237,12 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Friskt bäckdråg i naturskog</t>
+          <t>Örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3260,32 +3260,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128851789</v>
+        <v>128851785</v>
       </c>
       <c r="B26" t="n">
-        <v>92233</v>
+        <v>91558</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436183</v>
+        <v>436182</v>
       </c>
       <c r="R26" t="n">
-        <v>7004237</v>
+        <v>7004249</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Fuktigt bäckdråg i naturskog</t>
+          <t>Friskt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3464,32 +3464,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128851785</v>
+        <v>128851789</v>
       </c>
       <c r="B28" t="n">
-        <v>91551</v>
+        <v>92240</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3499,10 +3499,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436182</v>
+        <v>436183</v>
       </c>
       <c r="R28" t="n">
-        <v>7004249</v>
+        <v>7004237</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Friskt bäckdråg i naturskog</t>
+          <t>Fuktigt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3569,7 +3569,7 @@
         <v>128851795</v>
       </c>
       <c r="B29" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>128851792</v>
       </c>
       <c r="B30" t="n">
-        <v>91547</v>
+        <v>91554</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>128851794</v>
       </c>
       <c r="B32" t="n">
-        <v>91547</v>
+        <v>91554</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>128851790</v>
       </c>
       <c r="B33" t="n">
-        <v>88781</v>
+        <v>88788</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 34768-2025 artfynd.xlsx
+++ b/artfynd/A 34768-2025 artfynd.xlsx
@@ -2647,7 +2647,7 @@
         <v>128851784</v>
       </c>
       <c r="B20" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>128851793</v>
       </c>
       <c r="B21" t="n">
-        <v>83005</v>
+        <v>83007</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>128851787</v>
       </c>
       <c r="B22" t="n">
-        <v>57829</v>
+        <v>57831</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2950,48 +2950,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128851788</v>
+        <v>128851791</v>
       </c>
       <c r="B23" t="n">
-        <v>92869</v>
+        <v>91560</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5964</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436204</v>
+        <v>435967</v>
       </c>
       <c r="R23" t="n">
-        <v>7004134</v>
+        <v>7004356</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3032,13 +3029,12 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Friskt bäckdråg i naturskog</t>
+          <t>Gallrad grannaturskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3056,10 +3052,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128851791</v>
+        <v>128851786</v>
       </c>
       <c r="B24" t="n">
-        <v>91558</v>
+        <v>79041</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3067,21 +3063,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3091,10 +3087,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>435967</v>
+        <v>435927</v>
       </c>
       <c r="R24" t="n">
-        <v>7004356</v>
+        <v>7004337</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3140,7 +3136,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Gallrad grannaturskog</t>
+          <t>Örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3158,45 +3154,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128851786</v>
+        <v>128851788</v>
       </c>
       <c r="B25" t="n">
-        <v>79039</v>
+        <v>92871</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>435927</v>
+        <v>436204</v>
       </c>
       <c r="R25" t="n">
-        <v>7004337</v>
+        <v>7004134</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3237,12 +3236,13 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Örtrik grannaturskog</t>
+          <t>Friskt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3260,10 +3260,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128851785</v>
+        <v>128851796</v>
       </c>
       <c r="B26" t="n">
-        <v>91558</v>
+        <v>79041</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3271,21 +3271,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436182</v>
+        <v>436052</v>
       </c>
       <c r="R26" t="n">
-        <v>7004249</v>
+        <v>7004106</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Friskt bäckdråg i naturskog</t>
+          <t>Gallrad grannaturskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3362,32 +3362,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128851796</v>
+        <v>128851789</v>
       </c>
       <c r="B27" t="n">
-        <v>79039</v>
+        <v>92242</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3397,10 +3397,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436052</v>
+        <v>436183</v>
       </c>
       <c r="R27" t="n">
-        <v>7004106</v>
+        <v>7004237</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3446,7 +3446,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Gallrad grannaturskog</t>
+          <t>Fuktigt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3464,32 +3464,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128851789</v>
+        <v>128851785</v>
       </c>
       <c r="B28" t="n">
-        <v>92240</v>
+        <v>91560</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3499,10 +3499,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436183</v>
+        <v>436182</v>
       </c>
       <c r="R28" t="n">
-        <v>7004237</v>
+        <v>7004249</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Fuktigt bäckdråg i naturskog</t>
+          <t>Friskt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3569,7 +3569,7 @@
         <v>128851795</v>
       </c>
       <c r="B29" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>128851792</v>
       </c>
       <c r="B30" t="n">
-        <v>91554</v>
+        <v>91556</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         <v>128851783</v>
       </c>
       <c r="B31" t="n">
-        <v>78052</v>
+        <v>78054</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>128851794</v>
       </c>
       <c r="B32" t="n">
-        <v>91554</v>
+        <v>91556</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>128851790</v>
       </c>
       <c r="B33" t="n">
-        <v>88788</v>
+        <v>88790</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 34768-2025 artfynd.xlsx
+++ b/artfynd/A 34768-2025 artfynd.xlsx
@@ -3260,10 +3260,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128851796</v>
+        <v>128851785</v>
       </c>
       <c r="B26" t="n">
-        <v>79041</v>
+        <v>91560</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3271,21 +3271,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436052</v>
+        <v>436182</v>
       </c>
       <c r="R26" t="n">
-        <v>7004106</v>
+        <v>7004249</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Gallrad grannaturskog</t>
+          <t>Friskt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3362,32 +3362,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128851789</v>
+        <v>128851796</v>
       </c>
       <c r="B27" t="n">
-        <v>92242</v>
+        <v>79041</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3397,10 +3397,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436183</v>
+        <v>436052</v>
       </c>
       <c r="R27" t="n">
-        <v>7004237</v>
+        <v>7004106</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3446,7 +3446,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Fuktigt bäckdråg i naturskog</t>
+          <t>Gallrad grannaturskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3464,32 +3464,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128851785</v>
+        <v>128851789</v>
       </c>
       <c r="B28" t="n">
-        <v>91560</v>
+        <v>92242</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3499,10 +3499,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436182</v>
+        <v>436183</v>
       </c>
       <c r="R28" t="n">
-        <v>7004249</v>
+        <v>7004237</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Friskt bäckdråg i naturskog</t>
+          <t>Fuktigt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>

--- a/artfynd/A 34768-2025 artfynd.xlsx
+++ b/artfynd/A 34768-2025 artfynd.xlsx
@@ -2644,10 +2644,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128851784</v>
+        <v>128851793</v>
       </c>
       <c r="B20" t="n">
-        <v>91542</v>
+        <v>83007</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2655,21 +2655,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2679,10 +2679,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436212</v>
+        <v>435934</v>
       </c>
       <c r="R20" t="n">
-        <v>7004096</v>
+        <v>7004320</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Friskt bäckdråg i naturskog</t>
+          <t>Örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2746,10 +2746,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128851793</v>
+        <v>128851784</v>
       </c>
       <c r="B21" t="n">
-        <v>83007</v>
+        <v>91542</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2757,21 +2757,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2781,10 +2781,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>435934</v>
+        <v>436212</v>
       </c>
       <c r="R21" t="n">
-        <v>7004320</v>
+        <v>7004096</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Örtrik grannaturskog</t>
+          <t>Friskt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2950,45 +2950,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128851791</v>
+        <v>128851788</v>
       </c>
       <c r="B23" t="n">
-        <v>91560</v>
+        <v>92871</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>5964</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>435967</v>
+        <v>436204</v>
       </c>
       <c r="R23" t="n">
-        <v>7004356</v>
+        <v>7004134</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3029,12 +3032,13 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Gallrad grannaturskog</t>
+          <t>Friskt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3052,10 +3056,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128851786</v>
+        <v>128851791</v>
       </c>
       <c r="B24" t="n">
-        <v>79041</v>
+        <v>91560</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3063,21 +3067,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3087,10 +3091,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>435927</v>
+        <v>435967</v>
       </c>
       <c r="R24" t="n">
-        <v>7004337</v>
+        <v>7004356</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3136,7 +3140,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Örtrik grannaturskog</t>
+          <t>Gallrad grannaturskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3154,48 +3158,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128851788</v>
+        <v>128851786</v>
       </c>
       <c r="B25" t="n">
-        <v>92871</v>
+        <v>79041</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436204</v>
+        <v>435927</v>
       </c>
       <c r="R25" t="n">
-        <v>7004134</v>
+        <v>7004337</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3236,13 +3237,12 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Friskt bäckdråg i naturskog</t>
+          <t>Örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3260,10 +3260,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128851785</v>
+        <v>128851796</v>
       </c>
       <c r="B26" t="n">
-        <v>91560</v>
+        <v>79041</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3271,21 +3271,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436182</v>
+        <v>436052</v>
       </c>
       <c r="R26" t="n">
-        <v>7004249</v>
+        <v>7004106</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Friskt bäckdråg i naturskog</t>
+          <t>Gallrad grannaturskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3362,32 +3362,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128851796</v>
+        <v>128851789</v>
       </c>
       <c r="B27" t="n">
-        <v>79041</v>
+        <v>92242</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3397,10 +3397,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436052</v>
+        <v>436183</v>
       </c>
       <c r="R27" t="n">
-        <v>7004106</v>
+        <v>7004237</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3446,7 +3446,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Gallrad grannaturskog</t>
+          <t>Fuktigt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3464,32 +3464,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128851789</v>
+        <v>128851785</v>
       </c>
       <c r="B28" t="n">
-        <v>92242</v>
+        <v>91560</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3499,10 +3499,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436183</v>
+        <v>436182</v>
       </c>
       <c r="R28" t="n">
-        <v>7004237</v>
+        <v>7004249</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Fuktigt bäckdråg i naturskog</t>
+          <t>Friskt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>

--- a/artfynd/A 34768-2025 artfynd.xlsx
+++ b/artfynd/A 34768-2025 artfynd.xlsx
@@ -2644,10 +2644,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128851793</v>
+        <v>128851784</v>
       </c>
       <c r="B20" t="n">
-        <v>83007</v>
+        <v>91540</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2655,21 +2655,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2679,10 +2679,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>435934</v>
+        <v>436212</v>
       </c>
       <c r="R20" t="n">
-        <v>7004320</v>
+        <v>7004096</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Örtrik grannaturskog</t>
+          <t>Friskt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2746,10 +2746,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128851784</v>
+        <v>128851793</v>
       </c>
       <c r="B21" t="n">
-        <v>91542</v>
+        <v>83007</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2757,21 +2757,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2781,10 +2781,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436212</v>
+        <v>435934</v>
       </c>
       <c r="R21" t="n">
-        <v>7004096</v>
+        <v>7004320</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Friskt bäckdråg i naturskog</t>
+          <t>Örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2950,48 +2950,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128851788</v>
+        <v>128851786</v>
       </c>
       <c r="B23" t="n">
-        <v>92871</v>
+        <v>79041</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436204</v>
+        <v>435927</v>
       </c>
       <c r="R23" t="n">
-        <v>7004134</v>
+        <v>7004337</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3032,13 +3029,12 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Friskt bäckdråg i naturskog</t>
+          <t>Örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3059,7 +3055,7 @@
         <v>128851791</v>
       </c>
       <c r="B24" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3158,45 +3154,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128851786</v>
+        <v>128851788</v>
       </c>
       <c r="B25" t="n">
-        <v>79041</v>
+        <v>92857</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>435927</v>
+        <v>436204</v>
       </c>
       <c r="R25" t="n">
-        <v>7004337</v>
+        <v>7004134</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3237,12 +3236,13 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Örtrik grannaturskog</t>
+          <t>Friskt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3260,32 +3260,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128851796</v>
+        <v>128851789</v>
       </c>
       <c r="B26" t="n">
-        <v>79041</v>
+        <v>92257</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436052</v>
+        <v>436183</v>
       </c>
       <c r="R26" t="n">
-        <v>7004106</v>
+        <v>7004237</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Gallrad grannaturskog</t>
+          <t>Fuktigt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3362,32 +3362,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128851789</v>
+        <v>128851785</v>
       </c>
       <c r="B27" t="n">
-        <v>92242</v>
+        <v>91558</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3397,10 +3397,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436183</v>
+        <v>436182</v>
       </c>
       <c r="R27" t="n">
-        <v>7004237</v>
+        <v>7004249</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3446,7 +3446,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Fuktigt bäckdråg i naturskog</t>
+          <t>Friskt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3464,10 +3464,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128851785</v>
+        <v>128851796</v>
       </c>
       <c r="B28" t="n">
-        <v>91560</v>
+        <v>79041</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3475,21 +3475,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3499,10 +3499,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436182</v>
+        <v>436052</v>
       </c>
       <c r="R28" t="n">
-        <v>7004249</v>
+        <v>7004106</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Friskt bäckdråg i naturskog</t>
+          <t>Gallrad grannaturskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3569,7 +3569,7 @@
         <v>128851795</v>
       </c>
       <c r="B29" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>128851792</v>
       </c>
       <c r="B30" t="n">
-        <v>91556</v>
+        <v>91554</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3872,32 +3872,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128851794</v>
+        <v>128851790</v>
       </c>
       <c r="B32" t="n">
-        <v>91556</v>
+        <v>88791</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1204</v>
+        <v>4405</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436047</v>
+        <v>435918</v>
       </c>
       <c r="R32" t="n">
-        <v>7004126</v>
+        <v>7004318</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Örtrik grannaturskog</t>
+          <t>Futkigt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -3974,32 +3974,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128851790</v>
+        <v>128851794</v>
       </c>
       <c r="B33" t="n">
-        <v>88790</v>
+        <v>91554</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4405</v>
+        <v>1204</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4009,10 +4009,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>435918</v>
+        <v>436047</v>
       </c>
       <c r="R33" t="n">
-        <v>7004318</v>
+        <v>7004126</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Futkigt bäckdråg i naturskog</t>
+          <t>Örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>

--- a/artfynd/A 34768-2025 artfynd.xlsx
+++ b/artfynd/A 34768-2025 artfynd.xlsx
@@ -2644,10 +2644,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128851784</v>
+        <v>128851793</v>
       </c>
       <c r="B20" t="n">
-        <v>91540</v>
+        <v>83007</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2655,21 +2655,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2679,10 +2679,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436212</v>
+        <v>435934</v>
       </c>
       <c r="R20" t="n">
-        <v>7004096</v>
+        <v>7004320</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Friskt bäckdråg i naturskog</t>
+          <t>Örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2746,10 +2746,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128851793</v>
+        <v>128851784</v>
       </c>
       <c r="B21" t="n">
-        <v>83007</v>
+        <v>91540</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2757,21 +2757,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2781,10 +2781,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>435934</v>
+        <v>436212</v>
       </c>
       <c r="R21" t="n">
-        <v>7004320</v>
+        <v>7004096</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Örtrik grannaturskog</t>
+          <t>Friskt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2950,10 +2950,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128851786</v>
+        <v>128851791</v>
       </c>
       <c r="B23" t="n">
-        <v>79041</v>
+        <v>91560</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2961,23 +2961,19 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2985,10 +2981,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>435927</v>
+        <v>435967</v>
       </c>
       <c r="R23" t="n">
-        <v>7004337</v>
+        <v>7004356</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3034,7 +3030,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Örtrik grannaturskog</t>
+          <t>Gallrad grannaturskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3052,45 +3048,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128851791</v>
+        <v>128851788</v>
       </c>
       <c r="B24" t="n">
-        <v>91558</v>
+        <v>92858</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>5964</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>435967</v>
+        <v>436204</v>
       </c>
       <c r="R24" t="n">
-        <v>7004356</v>
+        <v>7004134</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3131,12 +3130,13 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Gallrad grannaturskog</t>
+          <t>Friskt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3154,48 +3154,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128851788</v>
+        <v>128851786</v>
       </c>
       <c r="B25" t="n">
-        <v>92857</v>
+        <v>79041</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436204</v>
+        <v>435927</v>
       </c>
       <c r="R25" t="n">
-        <v>7004134</v>
+        <v>7004337</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3236,13 +3233,12 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Friskt bäckdråg i naturskog</t>
+          <t>Örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3260,34 +3256,30 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128851789</v>
+        <v>128851785</v>
       </c>
       <c r="B26" t="n">
-        <v>92257</v>
+        <v>91560</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3295,10 +3287,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436183</v>
+        <v>436182</v>
       </c>
       <c r="R26" t="n">
-        <v>7004237</v>
+        <v>7004249</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3344,7 +3336,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Fuktigt bäckdråg i naturskog</t>
+          <t>Friskt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3362,10 +3354,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128851785</v>
+        <v>128851796</v>
       </c>
       <c r="B27" t="n">
-        <v>91558</v>
+        <v>79041</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3373,21 +3365,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3397,10 +3389,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436182</v>
+        <v>436052</v>
       </c>
       <c r="R27" t="n">
-        <v>7004249</v>
+        <v>7004106</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3446,7 +3438,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Friskt bäckdråg i naturskog</t>
+          <t>Gallrad grannaturskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3464,32 +3456,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128851796</v>
+        <v>128851789</v>
       </c>
       <c r="B28" t="n">
-        <v>79041</v>
+        <v>92258</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3499,10 +3491,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436052</v>
+        <v>436183</v>
       </c>
       <c r="R28" t="n">
-        <v>7004106</v>
+        <v>7004237</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3548,7 +3540,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Gallrad grannaturskog</t>
+          <t>Fuktigt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3569,7 +3561,7 @@
         <v>128851795</v>
       </c>
       <c r="B29" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3586,14 +3578,10 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>

--- a/artfynd/A 34768-2025 artfynd.xlsx
+++ b/artfynd/A 34768-2025 artfynd.xlsx
@@ -2644,10 +2644,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128851793</v>
+        <v>128851784</v>
       </c>
       <c r="B20" t="n">
-        <v>83007</v>
+        <v>91540</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2655,21 +2655,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2679,10 +2679,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>435934</v>
+        <v>436212</v>
       </c>
       <c r="R20" t="n">
-        <v>7004320</v>
+        <v>7004096</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Örtrik grannaturskog</t>
+          <t>Friskt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2746,10 +2746,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128851784</v>
+        <v>128851793</v>
       </c>
       <c r="B21" t="n">
-        <v>91540</v>
+        <v>83007</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2757,21 +2757,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2781,10 +2781,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436212</v>
+        <v>435934</v>
       </c>
       <c r="R21" t="n">
-        <v>7004096</v>
+        <v>7004320</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Friskt bäckdråg i naturskog</t>
+          <t>Örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3256,10 +3256,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128851785</v>
+        <v>128851796</v>
       </c>
       <c r="B26" t="n">
-        <v>91560</v>
+        <v>79041</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3267,19 +3267,23 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3287,10 +3291,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436182</v>
+        <v>436052</v>
       </c>
       <c r="R26" t="n">
-        <v>7004249</v>
+        <v>7004106</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3336,7 +3340,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Friskt bäckdråg i naturskog</t>
+          <t>Gallrad grannaturskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3354,32 +3358,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128851796</v>
+        <v>128851789</v>
       </c>
       <c r="B27" t="n">
-        <v>79041</v>
+        <v>92258</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3389,10 +3393,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436052</v>
+        <v>436183</v>
       </c>
       <c r="R27" t="n">
-        <v>7004106</v>
+        <v>7004237</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3438,7 +3442,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Gallrad grannaturskog</t>
+          <t>Fuktigt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3456,34 +3460,30 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128851789</v>
+        <v>128851785</v>
       </c>
       <c r="B28" t="n">
-        <v>92258</v>
+        <v>91560</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3491,10 +3491,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436183</v>
+        <v>436182</v>
       </c>
       <c r="R28" t="n">
-        <v>7004237</v>
+        <v>7004249</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3540,7 +3540,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Fuktigt bäckdråg i naturskog</t>
+          <t>Friskt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3860,32 +3860,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128851790</v>
+        <v>128851794</v>
       </c>
       <c r="B32" t="n">
-        <v>88791</v>
+        <v>91554</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4405</v>
+        <v>1204</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3895,10 +3895,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>435918</v>
+        <v>436047</v>
       </c>
       <c r="R32" t="n">
-        <v>7004318</v>
+        <v>7004126</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Futkigt bäckdråg i naturskog</t>
+          <t>Örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -3962,32 +3962,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128851794</v>
+        <v>128851790</v>
       </c>
       <c r="B33" t="n">
-        <v>91554</v>
+        <v>88791</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1204</v>
+        <v>4405</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436047</v>
+        <v>435918</v>
       </c>
       <c r="R33" t="n">
-        <v>7004126</v>
+        <v>7004318</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Örtrik grannaturskog</t>
+          <t>Futkigt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>

--- a/artfynd/A 34768-2025 artfynd.xlsx
+++ b/artfynd/A 34768-2025 artfynd.xlsx
@@ -2647,7 +2647,7 @@
         <v>128851784</v>
       </c>
       <c r="B20" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>128851793</v>
       </c>
       <c r="B21" t="n">
-        <v>83007</v>
+        <v>83011</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2950,41 +2950,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128851791</v>
+        <v>128851788</v>
       </c>
       <c r="B23" t="n">
-        <v>91560</v>
+        <v>92861</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>5964</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>435967</v>
+        <v>436204</v>
       </c>
       <c r="R23" t="n">
-        <v>7004356</v>
+        <v>7004134</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3025,12 +3032,13 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Gallrad grannaturskog</t>
+          <t>Friskt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3048,48 +3056,41 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128851788</v>
+        <v>128851791</v>
       </c>
       <c r="B24" t="n">
-        <v>92858</v>
+        <v>91563</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5964</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436204</v>
+        <v>435967</v>
       </c>
       <c r="R24" t="n">
-        <v>7004134</v>
+        <v>7004356</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3130,13 +3131,12 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Friskt bäckdråg i naturskog</t>
+          <t>Gallrad grannaturskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3157,7 +3157,7 @@
         <v>128851786</v>
       </c>
       <c r="B25" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3256,10 +3256,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128851796</v>
+        <v>128851785</v>
       </c>
       <c r="B26" t="n">
-        <v>79041</v>
+        <v>91563</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3267,23 +3267,19 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3291,10 +3287,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436052</v>
+        <v>436182</v>
       </c>
       <c r="R26" t="n">
-        <v>7004106</v>
+        <v>7004249</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3340,7 +3336,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Gallrad grannaturskog</t>
+          <t>Friskt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3361,7 +3357,7 @@
         <v>128851789</v>
       </c>
       <c r="B27" t="n">
-        <v>92258</v>
+        <v>92261</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3460,10 +3456,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128851785</v>
+        <v>128851796</v>
       </c>
       <c r="B28" t="n">
-        <v>91560</v>
+        <v>79043</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3471,19 +3467,23 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3491,10 +3491,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436182</v>
+        <v>436052</v>
       </c>
       <c r="R28" t="n">
-        <v>7004249</v>
+        <v>7004106</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3540,7 +3540,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Friskt bäckdråg i naturskog</t>
+          <t>Gallrad grannaturskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3561,7 +3561,7 @@
         <v>128851795</v>
       </c>
       <c r="B29" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>128851792</v>
       </c>
       <c r="B30" t="n">
-        <v>91554</v>
+        <v>91557</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         <v>128851783</v>
       </c>
       <c r="B31" t="n">
-        <v>78054</v>
+        <v>78056</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3860,32 +3860,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128851794</v>
+        <v>128851790</v>
       </c>
       <c r="B32" t="n">
-        <v>91554</v>
+        <v>88794</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1204</v>
+        <v>4405</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3895,10 +3895,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436047</v>
+        <v>435918</v>
       </c>
       <c r="R32" t="n">
-        <v>7004126</v>
+        <v>7004318</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Örtrik grannaturskog</t>
+          <t>Futkigt bäckdråg i naturskog</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -3962,32 +3962,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128851790</v>
+        <v>128851794</v>
       </c>
       <c r="B33" t="n">
-        <v>88791</v>
+        <v>91557</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4405</v>
+        <v>1204</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>435918</v>
+        <v>436047</v>
       </c>
       <c r="R33" t="n">
-        <v>7004318</v>
+        <v>7004126</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Futkigt bäckdråg i naturskog</t>
+          <t>Örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>

--- a/artfynd/A 34768-2025 artfynd.xlsx
+++ b/artfynd/A 34768-2025 artfynd.xlsx
@@ -1608,7 +1608,7 @@
         <v>126976640</v>
       </c>
       <c r="B10" t="n">
-        <v>57823</v>
+        <v>57817</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>126976115</v>
       </c>
       <c r="B11" t="n">
-        <v>79099</v>
+        <v>79090</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>127013820</v>
       </c>
       <c r="B12" t="n">
-        <v>91346</v>
+        <v>91333</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>127013821</v>
       </c>
       <c r="B13" t="n">
-        <v>91350</v>
+        <v>91337</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2022,10 +2022,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126976053</v>
+        <v>127013813</v>
       </c>
       <c r="B14" t="n">
-        <v>88735</v>
+        <v>57672</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2033,21 +2033,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2057,10 +2057,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436013</v>
+        <v>436103</v>
       </c>
       <c r="R14" t="n">
-        <v>7004046</v>
+        <v>7004242</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2090,19 +2090,14 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>11:39</t>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2117,22 +2112,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Johan Råghall, Benny Öwre</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126977038</v>
+        <v>126976053</v>
       </c>
       <c r="B15" t="n">
-        <v>91332</v>
+        <v>88722</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2140,21 +2135,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2164,10 +2159,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436141</v>
+        <v>436013</v>
       </c>
       <c r="R15" t="n">
-        <v>7004306</v>
+        <v>7004046</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2199,7 +2194,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2209,7 +2204,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2236,10 +2231,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127013818</v>
+        <v>127013812</v>
       </c>
       <c r="B16" t="n">
-        <v>79099</v>
+        <v>57672</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2247,21 +2242,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2271,10 +2266,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436018</v>
+        <v>435955</v>
       </c>
       <c r="R16" t="n">
-        <v>7004046</v>
+        <v>7004281</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2307,6 +2302,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2333,10 +2333,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126976710</v>
+        <v>127013818</v>
       </c>
       <c r="B17" t="n">
-        <v>91350</v>
+        <v>79090</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2344,21 +2344,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2368,13 +2368,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436064</v>
+        <v>436018</v>
       </c>
       <c r="R17" t="n">
-        <v>7004111</v>
+        <v>7004046</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2401,19 +2401,9 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>12:01</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>12:01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2428,22 +2418,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Johan Råghall, Benny Öwre</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127013813</v>
+        <v>126977038</v>
       </c>
       <c r="B18" t="n">
-        <v>57672</v>
+        <v>91319</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2451,21 +2441,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2475,10 +2465,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436103</v>
+        <v>436141</v>
       </c>
       <c r="R18" t="n">
-        <v>7004242</v>
+        <v>7004306</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2508,14 +2498,19 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2530,22 +2525,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall, Benny Öwre</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127013812</v>
+        <v>126976710</v>
       </c>
       <c r="B19" t="n">
-        <v>57672</v>
+        <v>91337</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2553,21 +2548,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2577,13 +2572,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>435955</v>
+        <v>436064</v>
       </c>
       <c r="R19" t="n">
-        <v>7004281</v>
+        <v>7004111</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2610,14 +2605,19 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2632,12 +2632,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall, Benny Öwre</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 34768-2025 artfynd.xlsx
+++ b/artfynd/A 34768-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89593716</v>
+        <v>126976053</v>
       </c>
       <c r="B2" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Järvdalen utökn öst, Jmt</t>
+          <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>435960.8660408962</v>
+        <v>436013</v>
       </c>
       <c r="R2" t="n">
-        <v>7004281.893633313</v>
+        <v>7004046</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-09-03</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-09-17</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,31 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Johan Råghall, Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89593678</v>
+        <v>126976115</v>
       </c>
       <c r="B3" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Järvdalen utökn öst, Jmt</t>
+          <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>435960.8660408962</v>
+        <v>436013</v>
       </c>
       <c r="R3" t="n">
-        <v>7004281.893633313</v>
+        <v>7004046</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,22 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-09-03</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-09-17</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,31 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Johan Råghall, Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89593692</v>
+        <v>126976389</v>
       </c>
       <c r="B4" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,34 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Järvdalen utökn öst, Jmt</t>
+          <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>435960.8660408962</v>
+        <v>436001</v>
       </c>
       <c r="R4" t="n">
-        <v>7004281.893633313</v>
+        <v>7004090</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,27 +954,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-09-03</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-09-17</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,66 +984,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Johan Råghall, Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89593695</v>
+        <v>127013817</v>
       </c>
       <c r="B5" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221952</v>
+        <v>864</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Järvdalen utökn öst, Jmt</t>
+          <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>435960.8660408962</v>
+        <v>435951</v>
       </c>
       <c r="R5" t="n">
-        <v>7004281.893633313</v>
+        <v>7004241</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,22 +1061,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-09-03</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-09-17</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,31 +1081,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>89593682</v>
+        <v>127013818</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,34 +1104,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Järvdalen utökn öst, Jmt</t>
+          <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>435960.8660408962</v>
+        <v>436018</v>
       </c>
       <c r="R6" t="n">
-        <v>7004281.893633313</v>
+        <v>7004046</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,22 +1158,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-09-03</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-09-17</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,40 +1174,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Finns sporadiskt på de granar som står kvar.</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>89593724</v>
+        <v>126977038</v>
       </c>
       <c r="B7" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1281,34 +1201,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Järvdalen utökn öst, Jmt</t>
+          <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>435960.8660408962</v>
+        <v>436141</v>
       </c>
       <c r="R7" t="n">
-        <v>7004281.893633313</v>
+        <v>7004306</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,22 +1255,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2020-09-03</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2020-09-17</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,53 +1285,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Johan Råghall, Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>95218594</v>
+        <v>127013811</v>
       </c>
       <c r="B8" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1421,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>435989.4806460959</v>
+        <v>435951</v>
       </c>
       <c r="R8" t="n">
-        <v>7004424.151396832</v>
+        <v>7004242</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,22 +1362,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-07-17</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-07-17</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1493,37 +1394,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>95218593</v>
+        <v>128851784</v>
       </c>
       <c r="B9" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1533,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>435973.6999981949</v>
+        <v>436212</v>
       </c>
       <c r="R9" t="n">
-        <v>7004427.175613223</v>
+        <v>7004096</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,22 +1459,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-07-17</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-07-17</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1589,73 +1475,69 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Friskt bäckdråg i naturskog</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126976640</v>
+        <v>89593724</v>
       </c>
       <c r="B10" t="n">
-        <v>57823</v>
+        <v>91923</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mårdsundsbodarna, Jmt</t>
+          <t>Järvdalen utökn öst, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436064</v>
+        <v>435961</v>
       </c>
       <c r="R10" t="n">
-        <v>7004111</v>
+        <v>7004282</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1679,22 +1561,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:59</t>
+          <t>2020-09-03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:59</t>
+          <t>2020-09-17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1709,44 +1581,48 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Johan Råghall, Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126976115</v>
+        <v>127013820</v>
       </c>
       <c r="B11" t="n">
-        <v>79099</v>
+        <v>91923</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>864</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1756,10 +1632,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436013</v>
+        <v>436027</v>
       </c>
       <c r="R11" t="n">
-        <v>7004046</v>
+        <v>7004044</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1789,19 +1665,9 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:39</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1816,26 +1682,26 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Johan Råghall, Benny Öwre</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127013820</v>
+        <v>128851792</v>
       </c>
       <c r="B12" t="n">
-        <v>91346</v>
+        <v>91923</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1863,10 +1729,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436027</v>
+        <v>436194</v>
       </c>
       <c r="R12" t="n">
-        <v>7004044</v>
+        <v>7004198</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1893,12 +1759,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1909,48 +1775,53 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Örtrik grannaturskog</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127013821</v>
+        <v>128851794</v>
       </c>
       <c r="B13" t="n">
-        <v>91350</v>
+        <v>91923</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1960,10 +1831,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436158</v>
+        <v>436047</v>
       </c>
       <c r="R13" t="n">
-        <v>7004285</v>
+        <v>7004126</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1990,12 +1861,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2006,26 +1877,31 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Örtrik grannaturskog</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126976053</v>
+        <v>89593678</v>
       </c>
       <c r="B14" t="n">
-        <v>88735</v>
+        <v>83173</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2033,34 +1909,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>510</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mårdsundsbodarna, Jmt</t>
+          <t>Järvdalen utökn öst, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436013</v>
+        <v>435961</v>
       </c>
       <c r="R14" t="n">
-        <v>7004046</v>
+        <v>7004282</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2087,22 +1963,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>11:39</t>
+          <t>2020-09-03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>11:39</t>
+          <t>2020-09-17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2117,44 +1983,48 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Johan Råghall, Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126977038</v>
+        <v>128851789</v>
       </c>
       <c r="B15" t="n">
-        <v>91332</v>
+        <v>92632</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2164,10 +2034,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436141</v>
+        <v>436183</v>
       </c>
       <c r="R15" t="n">
-        <v>7004306</v>
+        <v>7004237</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2194,22 +2064,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:16</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:16</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2220,48 +2080,53 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Fuktigt bäckdråg i naturskog</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Johan Råghall, Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127013818</v>
+        <v>128851790</v>
       </c>
       <c r="B16" t="n">
-        <v>79099</v>
+        <v>89143</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>864</v>
+        <v>4405</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2271,10 +2136,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436018</v>
+        <v>435918</v>
       </c>
       <c r="R16" t="n">
-        <v>7004046</v>
+        <v>7004318</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2301,12 +2166,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2317,26 +2182,31 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Futkigt bäckdråg i naturskog</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126976710</v>
+        <v>128851788</v>
       </c>
       <c r="B17" t="n">
-        <v>91350</v>
+        <v>93233</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2344,37 +2214,40 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>5964</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436064</v>
+        <v>436204</v>
       </c>
       <c r="R17" t="n">
-        <v>7004111</v>
+        <v>7004134</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2398,22 +2271,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>12:01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>12:01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2422,63 +2285,69 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Friskt bäckdråg i naturskog</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Johan Råghall, Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127013813</v>
+        <v>89593682</v>
       </c>
       <c r="B18" t="n">
-        <v>57672</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mårdsundsbodarna, Jmt</t>
+          <t>Järvdalen utökn öst, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436103</v>
+        <v>435961</v>
       </c>
       <c r="R18" t="n">
-        <v>7004242</v>
+        <v>7004282</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2505,17 +2374,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2020-09-03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2020-09-17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2526,48 +2390,57 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Finns sporadiskt på de granar som står kvar.</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127013812</v>
+        <v>128851786</v>
       </c>
       <c r="B19" t="n">
-        <v>57672</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2577,10 +2450,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>435955</v>
+        <v>435927</v>
       </c>
       <c r="R19" t="n">
-        <v>7004281</v>
+        <v>7004337</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2607,17 +2480,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2628,48 +2496,53 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Örtrik grannaturskog</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128851784</v>
+        <v>128851796</v>
       </c>
       <c r="B20" t="n">
-        <v>91543</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2679,10 +2552,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436212</v>
+        <v>436052</v>
       </c>
       <c r="R20" t="n">
-        <v>7004096</v>
+        <v>7004106</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2728,7 +2601,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Friskt bäckdråg i naturskog</t>
+          <t>Gallrad grannaturskog</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2749,7 +2622,7 @@
         <v>128851793</v>
       </c>
       <c r="B21" t="n">
-        <v>83011</v>
+        <v>83307</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2848,10 +2721,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128851787</v>
+        <v>89593716</v>
       </c>
       <c r="B22" t="n">
-        <v>57831</v>
+        <v>80461</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2859,34 +2732,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103031</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mårdsundsbodarna, Jmt</t>
+          <t>Järvdalen utökn öst, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436100</v>
+        <v>435961</v>
       </c>
       <c r="R22" t="n">
-        <v>7004195</v>
+        <v>7004282</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2913,12 +2786,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2020-09-03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2020-09-17</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2929,69 +2802,65 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Gallrad grannaturskog</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128851788</v>
+        <v>89593692</v>
       </c>
       <c r="B23" t="n">
-        <v>92861</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5964</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mårdsundsbodarna, Jmt</t>
+          <t>Järvdalen utökn öst, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436204</v>
+        <v>435961</v>
       </c>
       <c r="R23" t="n">
-        <v>7004134</v>
+        <v>7004282</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3018,12 +2887,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2020-09-03</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2020-09-17</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3032,34 +2906,32 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Friskt bäckdråg i naturskog</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128851791</v>
+        <v>127013812</v>
       </c>
       <c r="B24" t="n">
-        <v>91563</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3067,19 +2939,23 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3087,10 +2963,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>435967</v>
+        <v>435955</v>
       </c>
       <c r="R24" t="n">
-        <v>7004356</v>
+        <v>7004281</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3117,12 +2993,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3133,31 +3014,26 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Gallrad grannaturskog</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128851786</v>
+        <v>127013813</v>
       </c>
       <c r="B25" t="n">
-        <v>79043</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3165,21 +3041,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3189,10 +3065,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>435927</v>
+        <v>436103</v>
       </c>
       <c r="R25" t="n">
-        <v>7004337</v>
+        <v>7004242</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3219,12 +3095,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3235,31 +3116,26 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>Örtrik grannaturskog</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128851785</v>
+        <v>127013814</v>
       </c>
       <c r="B26" t="n">
-        <v>91563</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3267,19 +3143,23 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3287,10 +3167,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436182</v>
+        <v>436062</v>
       </c>
       <c r="R26" t="n">
-        <v>7004249</v>
+        <v>7004170</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3317,12 +3197,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3333,31 +3218,26 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Friskt bäckdråg i naturskog</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128851789</v>
+        <v>89593693</v>
       </c>
       <c r="B27" t="n">
-        <v>92261</v>
+        <v>57141</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3365,34 +3245,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3298</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Mårdsundsbodarna, Jmt</t>
+          <t>Järvdalen utökn öst, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436183</v>
+        <v>435961</v>
       </c>
       <c r="R27" t="n">
-        <v>7004237</v>
+        <v>7004282</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3419,12 +3299,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2020-09-03</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2020-09-17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3435,31 +3315,30 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Fuktigt bäckdråg i naturskog</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128851796</v>
+        <v>126976640</v>
       </c>
       <c r="B28" t="n">
-        <v>79043</v>
+        <v>58114</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3467,37 +3346,46 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Mårdsundsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436052</v>
+        <v>436064</v>
       </c>
       <c r="R28" t="n">
-        <v>7004106</v>
+        <v>7004111</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3521,12 +3409,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3537,31 +3435,26 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>Gallrad grannaturskog</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Johan Råghall, Benny Öwre</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128851795</v>
+        <v>95218602</v>
       </c>
       <c r="B29" t="n">
-        <v>91563</v>
+        <v>58057</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3569,19 +3462,23 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>103031</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3589,10 +3486,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436052</v>
+        <v>435975</v>
       </c>
       <c r="R29" t="n">
-        <v>7004105</v>
+        <v>7004418</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3619,12 +3516,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2021-07-17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2021-07-17</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3635,31 +3532,26 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>Gallrad grannaturskog</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128851792</v>
+        <v>128851787</v>
       </c>
       <c r="B30" t="n">
-        <v>91557</v>
+        <v>58057</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3667,21 +3559,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1204</v>
+        <v>103031</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3691,10 +3583,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436194</v>
+        <v>436100</v>
       </c>
       <c r="R30" t="n">
-        <v>7004198</v>
+        <v>7004195</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3740,7 +3632,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Örtrik grannaturskog</t>
+          <t>Gallrad grannaturskog</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3758,32 +3650,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128851783</v>
+        <v>126976228</v>
       </c>
       <c r="B31" t="n">
-        <v>78056</v>
+        <v>99035</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228579</v>
+        <v>219790</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3793,10 +3685,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>435934</v>
+        <v>435990</v>
       </c>
       <c r="R31" t="n">
-        <v>7004320</v>
+        <v>7004061</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3823,12 +3715,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3839,31 +3741,26 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>Fuktigt bäckdråg i naturskog</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Johan Råghall, Benny Öwre</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128851790</v>
+        <v>89593695</v>
       </c>
       <c r="B32" t="n">
-        <v>88794</v>
+        <v>99140</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3871,34 +3768,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4405</v>
+        <v>221952</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mårdsundsbodarna, Jmt</t>
+          <t>Järvdalen utökn öst, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>435918</v>
+        <v>435961</v>
       </c>
       <c r="R32" t="n">
-        <v>7004318</v>
+        <v>7004282</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3925,12 +3822,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2020-09-03</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2020-09-17</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3941,53 +3838,52 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>Futkigt bäckdråg i naturskog</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128851794</v>
+        <v>95218593</v>
       </c>
       <c r="B33" t="n">
-        <v>91557</v>
+        <v>99140</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1204</v>
+        <v>221952</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3997,10 +3893,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436047</v>
+        <v>435974</v>
       </c>
       <c r="R33" t="n">
-        <v>7004126</v>
+        <v>7004427</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4027,12 +3923,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2021-07-17</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2021-07-17</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4043,24 +3939,325 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>Örtrik grannaturskog</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>95218594</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Mårdsundsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>435990</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7004424</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2021-07-17</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2021-07-17</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128851783</v>
+      </c>
+      <c r="B35" t="n">
+        <v>78339</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Mårdsundsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>435934</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7004320</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Fuktigt bäckdråg i naturskog</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
           <t>Rashid Kadhim</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
+      <c r="AX35" t="inlineStr">
         <is>
           <t>Rashid Kadhim</t>
         </is>
       </c>
-      <c r="AY33" t="inlineStr"/>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>126977342</v>
+      </c>
+      <c r="B36" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Mårdsundsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>435950</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7004235</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34768-2025 artfynd.xlsx
+++ b/artfynd/A 34768-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126976053</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126976115</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126976389</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127013817</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127013818</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1294,6 +1324,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126977038</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1391,6 +1426,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127013811</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1493,6 +1533,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128851784</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1594,6 +1639,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89593724</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1691,6 +1741,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127013820</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1793,6 +1848,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128851792</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1895,6 +1955,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128851794</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1996,6 +2061,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89593678</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2098,6 +2168,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128851789</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2200,6 +2275,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128851790</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2306,6 +2386,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128851788</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2412,6 +2497,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89593682</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2514,6 +2604,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128851786</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2616,6 +2711,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128851796</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2718,6 +2818,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128851793</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2819,6 +2924,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89593716</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2925,6 +3035,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89593692</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3027,6 +3142,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127013812</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3129,6 +3249,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127013813</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3231,6 +3356,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127013814</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3332,6 +3462,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89593693</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3448,6 +3583,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126976640</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3545,6 +3685,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95218602</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3647,6 +3792,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128851787</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3754,6 +3904,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126976228</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3855,6 +4010,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89593695</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3952,6 +4112,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95218593</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4049,6 +4214,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95218594</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4151,6 +4321,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128851783</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4258,8 +4433,50 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126977342</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>